--- a/workshop_registration_form_templates/006_treasury_digitalization_program_registration--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/006_treasury_digitalization_program_registration--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>America/New_York</t>
+          <t>America/New York</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>America/Los Angeles</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>america/los_angeles</t>
+          <t>europe/london</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>America/Los_Angeles</t>
+          <t>Europe/London</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>europe/london</t>
+          <t>australia/perth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe/London</t>
+          <t>Australia/Perth</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>australia/perth</t>
+          <t>america/indianapolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australia/Perth</t>
+          <t>America/Indianapolis</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>america/indianapolis</t>
+          <t>america/denver</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>America/Indianapolis</t>
+          <t>America/Denver</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>america/chicago</t>
+          <t>america/vancouver</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>America/Chicago</t>
+          <t>America/Vancouver</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>america/denver</t>
+          <t>asia/calcutta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>America/Denver</t>
+          <t>Asia/Calcutta</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>america/new_york</t>
+          <t>asia/dubai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>America/New_York</t>
+          <t>Asia/Dubai</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>america/indianapolis</t>
+          <t>australia/melbourne</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>America/Indianapolis</t>
+          <t>Australia/Melbourne</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>america/vancouver</t>
+          <t>asia/beijing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>America/Vancouver</t>
+          <t>Asia/Beijing</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>asia/calcutta</t>
+          <t>europe/madrid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Asia/Calcutta</t>
+          <t>Europe/Madrid</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>asia/dubai</t>
+          <t>asia/mumbai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Asia/Dubai</t>
+          <t>Asia/Mumbai</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>australia/melbourne</t>
+          <t>america/san_francisco</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Australia/Melbourne</t>
+          <t>America/San Francisco</t>
         </is>
       </c>
     </row>
@@ -1258,78 +1258,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>asia/beijing</t>
+          <t>america/seattle</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>Asia/Beijing</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>europe/madrid</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Europe/Madrid</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>asia/mumbai</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Asia/Mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>america/san_francisco</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>America/San_Francisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>america/seattle</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>America/Seattle</t>
         </is>
